--- a/data/annotations_export.xlsx
+++ b/data/annotations_export.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -889,9 +889,114 @@
         <v>Dr Essafi</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>IDRiD_073.jpg</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>IDRiD_073test.jpg</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.7</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>IDRiD_014test.jpg</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.3</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Dr Hafidi</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/annotations_export.xlsx
+++ b/data/annotations_export.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -994,9 +994,394 @@
         <v>Dr Hafidi</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>IDRiD_074.jpg</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>IDRiD_074test.jpg</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>IDRiD_075.jpg</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>IDRiD_076.jpg</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>IDRiD_076test.jpg</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.7</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>IDRiD_077.jpg</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>IDRiD_078.jpg</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.7</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>IDRiD_078test.jpg</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.3</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>IDRiD_079.jpg</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.7</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>IDRiD_079test.jpg</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.3</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>IDRiD_080.jpg</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K28"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/annotations_export.xlsx
+++ b/data/annotations_export.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -751,13 +751,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>IDRiD_295.jpg</v>
+        <v>IDRiD_071.jpg</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -778,30 +778,30 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="str">
-        <v>Dr Boulanouar</v>
+        <v>Dr Essafi</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>IDRiD_071.jpg</v>
+        <v>IDRiD_072.jpg</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K12" t="str">
         <v>Dr Essafi</v>
@@ -821,22 +821,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>IDRiD_072.jpg</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
+        <v>IDRiD_072test.jpg</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="K13" t="str">
         <v>Dr Essafi</v>
@@ -856,22 +856,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>IDRiD_072test.jpg</v>
-      </c>
-      <c r="B14" t="str">
-        <v/>
+        <v>IDRiD_073.jpg</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="K14" t="str">
         <v>Dr Essafi</v>
@@ -891,7 +891,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>IDRiD_073.jpg</v>
+        <v>IDRiD_073test.jpg</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -903,7 +903,7 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K15" t="str">
         <v>Dr Essafi</v>
@@ -926,22 +926,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>IDRiD_073test.jpg</v>
+        <v>IDRiD_014test.jpg</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -953,18 +953,18 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="K16" t="str">
-        <v>Dr Essafi</v>
+        <v>Dr Hafidi</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>IDRiD_014test.jpg</v>
+        <v>IDRiD_074.jpg</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -988,15 +988,15 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="K17" t="str">
-        <v>Dr Hafidi</v>
+        <v>Dr Essafi</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>IDRiD_074.jpg</v>
+        <v>IDRiD_074test.jpg</v>
       </c>
       <c r="B18">
         <v>4</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>IDRiD_074test.jpg</v>
+        <v>IDRiD_075.jpg</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -1066,16 +1066,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>IDRiD_075.jpg</v>
+        <v>IDRiD_076.jpg</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>IDRiD_076.jpg</v>
+        <v>IDRiD_076test.jpg</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K21" t="str">
         <v>Dr Essafi</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>IDRiD_076test.jpg</v>
+        <v>IDRiD_077.jpg</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1151,10 +1151,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1163,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K22" t="str">
         <v>Dr Essafi</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>IDRiD_077.jpg</v>
+        <v>IDRiD_078.jpg</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1198,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K23" t="str">
         <v>Dr Essafi</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>IDRiD_078.jpg</v>
+        <v>IDRiD_078test.jpg</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -1227,13 +1227,13 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="K24" t="str">
         <v>Dr Essafi</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>IDRiD_078test.jpg</v>
+        <v>IDRiD_079.jpg</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -1259,16 +1259,16 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="str">
         <v>Dr Essafi</v>
@@ -1276,7 +1276,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>IDRiD_079.jpg</v>
+        <v>IDRiD_079test.jpg</v>
       </c>
       <c r="B26">
         <v>3</v>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="K26" t="str">
         <v>Dr Essafi</v>
@@ -1311,16 +1311,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>IDRiD_079test.jpg</v>
+        <v>IDRiD_080.jpg</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="K27" t="str">
         <v>Dr Essafi</v>
@@ -1346,16 +1346,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>IDRiD_080.jpg</v>
+        <v>IDRiD_080test.jpg</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -1373,15 +1373,610 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>IDRiD_081.jpg</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.7</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>IDRiD_096test.jpg</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>IDRiD_097.jpg</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.3</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>IDRiD_098.jpg</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>IDRiD_099.jpg</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>IDRiD_100.jpg</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>IDRiD_100test.jpg</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.7</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>IDRiD_101.jpg</v>
+      </c>
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.7</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>IDRiD_101test.jpg</v>
+      </c>
+      <c r="B37">
+        <v>3</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.7</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>IDRiD_102.jpg</v>
+      </c>
+      <c r="B38">
+        <v>3</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>IDRiD_102test.jpg</v>
+      </c>
+      <c r="B39">
+        <v>3</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.3</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>IDRiD_103.jpg</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.3</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>IDRiD_103test.jpg</v>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>0.3</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>IDRiD_104.jpg</v>
+      </c>
+      <c r="B42">
+        <v>3</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.7</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>IDRiD_105.jpg</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.7</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>IDRiD_106.jpg</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.3</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Dr Essafi</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>IDRiD_107.jpg</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45" t="str">
         <v>Dr Essafi</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K45"/>
   </ignoredErrors>
 </worksheet>
 </file>